--- a/PPREstimation/output/top10/47_2_East_China_Sea_(2018).xlsx
+++ b/PPREstimation/output/top10/47_2_East_China_Sea_(2018).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -701,7 +700,6 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>3.939221707223617</v>
       </c>
@@ -869,7 +866,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>4.236350399264976</v>
       </c>
@@ -953,7 +949,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>3.205734197347111</v>
       </c>
@@ -1037,7 +1032,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>3.498127357177683</v>
       </c>
@@ -1121,7 +1115,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>3.434516952291139</v>
       </c>
@@ -1205,7 +1198,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>3.459206316720225</v>
       </c>
@@ -1289,7 +1281,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>3.522168023967968</v>
       </c>
@@ -1373,7 +1364,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>2.964159068931464</v>
       </c>
@@ -1457,7 +1447,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
         <v>3.419154493005507</v>
       </c>
@@ -1541,7 +1530,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
         <v>3.368417039620239</v>
       </c>
@@ -1625,7 +1613,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
         <v>3.939908374737592</v>
       </c>
@@ -1709,7 +1696,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
         <v>2.874922941578929</v>
       </c>
@@ -1793,7 +1779,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
         <v>2.919098558167094</v>
       </c>
@@ -1877,7 +1862,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
         <v>2.95490985581671</v>
       </c>
@@ -1961,7 +1945,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
         <v>2.314</v>
       </c>
@@ -2045,7 +2028,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
         <v>2.333908</v>
       </c>
@@ -2129,7 +2111,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
         <v>2</v>
       </c>
@@ -2213,7 +2194,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
         <v>2.21198320166959</v>
       </c>
@@ -2297,7 +2277,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
         <v>2.150698795180723</v>
       </c>
@@ -2381,7 +2360,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
         <v>2.168674698795181</v>
       </c>
@@ -2465,7 +2443,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
         <v>2</v>
       </c>
@@ -2549,7 +2526,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
         <v>2</v>
       </c>
@@ -2633,7 +2609,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
@@ -2709,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2847,6 +2822,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2857,9 +2842,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -2890,19 +2872,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2915,9 +2897,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -2967,6 +2946,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2979,11 +2961,8 @@
           <t>Marine mammals</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>2.059823057548223</v>
+        <v>3646.690246215947</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -2991,7 +2970,6 @@
       <c r="H4" s="2" t="n">
         <v>115.3593706581089</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -3030,6 +3008,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>576.764203308484</v>
       </c>
     </row>
     <row r="5">
@@ -3041,11 +3022,8 @@
           <t>Sharks</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>2.064373367881418</v>
+        <v>7158.210267951511</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -3053,7 +3031,6 @@
       <c r="H5" s="2" t="n">
         <v>132.6519786385593</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
@@ -3092,6 +3069,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>957.9520771989784</v>
       </c>
     </row>
     <row r="6">
@@ -3103,11 +3083,8 @@
           <t>Small yellow croakers</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>1.575315102130983</v>
+        <v>417.3596931254341</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>47.42354941555242</v>
@@ -3156,6 +3133,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>55.91025171370618</v>
+      </c>
+      <c r="X6" t="n">
+        <v>100.1055867877105</v>
       </c>
     </row>
     <row r="7">
@@ -3167,11 +3147,8 @@
           <t>Large yellow croakers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>1.50727242138883</v>
+        <v>779.1224198818753</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>192.2445438810318</v>
@@ -3220,6 +3197,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>209.9865978495988</v>
+      </c>
+      <c r="X7" t="n">
+        <v>174.4013401687511</v>
       </c>
     </row>
     <row r="8">
@@ -3231,11 +3211,8 @@
           <t>Omnivores</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>1.610842023763221</v>
+        <v>618.2129176215519</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>66.74783897385331</v>
@@ -3284,6 +3261,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>96.76225383152892</v>
+      </c>
+      <c r="X8" t="n">
+        <v>148.0416060918919</v>
       </c>
     </row>
     <row r="9">
@@ -3295,11 +3275,8 @@
           <t>Benthivores/piscivores</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>1.521439154553365</v>
+        <v>1801.92419656322</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>177.8829227516127</v>
@@ -3348,6 +3325,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>223.950572839607</v>
+      </c>
+      <c r="X9" t="n">
+        <v>303.366600965259</v>
       </c>
     </row>
     <row r="10">
@@ -3359,11 +3339,8 @@
           <t>Planktivores/piscivores</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>1.717502381380568</v>
+        <v>843.6086183402634</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>376.4866487287316</v>
@@ -3412,6 +3389,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>569.9559065810146</v>
+      </c>
+      <c r="X10" t="n">
+        <v>186.3051806929205</v>
       </c>
     </row>
     <row r="11">
@@ -3423,11 +3403,8 @@
           <t>Planktivores/Benthivores</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>1.498846303097567</v>
+        <v>100.3306223433815</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>161.7610669209278</v>
@@ -3476,6 +3453,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>162.9779414942278</v>
+      </c>
+      <c r="X11" t="n">
+        <v>39.2787421615364</v>
       </c>
     </row>
     <row r="12">
@@ -3487,11 +3467,8 @@
           <t>Bombay duck</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>0.993473016568215</v>
+        <v>346.3430111879682</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>45.51131434280686</v>
@@ -3540,6 +3517,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>292.0676467422069</v>
+      </c>
+      <c r="X12" t="n">
+        <v>84.90723119902714</v>
       </c>
     </row>
     <row r="13">
@@ -3551,11 +3531,8 @@
           <t>Hairtails</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>1.495637617613781</v>
+        <v>435.597009623415</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>99.69425304042275</v>
@@ -3604,6 +3581,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>259.9440427523834</v>
+      </c>
+      <c r="X13" t="n">
+        <v>105.8030308475263</v>
       </c>
     </row>
     <row r="14">
@@ -3615,11 +3595,8 @@
           <t>Piscivores</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>1.876572256470499</v>
+        <v>1545.281225484078</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>533.3412604286061</v>
@@ -3668,6 +3645,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>743.6342078036779</v>
+      </c>
+      <c r="X14" t="n">
+        <v>317.21368645339</v>
       </c>
     </row>
     <row r="15">
@@ -3679,11 +3659,8 @@
           <t>Benthivores</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>0.8547228378669564</v>
+        <v>135.9331941983532</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>29.53511154951039</v>
@@ -3732,6 +3709,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>112.3495751915816</v>
+      </c>
+      <c r="X15" t="n">
+        <v>38.72731943586039</v>
       </c>
     </row>
     <row r="16">
@@ -3743,11 +3723,8 @@
           <t>Planktivores</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>1.247049333001273</v>
+        <v>89.11749090339191</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>39.28365681564409</v>
@@ -3796,6 +3773,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>45.01021813841825</v>
+      </c>
+      <c r="X16" t="n">
+        <v>34.03926893952787</v>
       </c>
     </row>
     <row r="17">
@@ -3807,11 +3787,8 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>1.491852169698695</v>
+        <v>184.195986793919</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>41.62243119638905</v>
@@ -3860,6 +3837,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>43.92231206048399</v>
+      </c>
+      <c r="X17" t="n">
+        <v>56.8332479635069</v>
       </c>
     </row>
     <row r="18">
@@ -3871,11 +3851,8 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>0.5235411757885634</v>
+        <v>21.1696376984914</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>8.013251062020991</v>
@@ -3924,6 +3901,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>8.164809927598361</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8.854653913237232</v>
       </c>
     </row>
     <row r="19">
@@ -3935,11 +3915,8 @@
           <t>Crabs</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>0.5594931966461811</v>
+        <v>22.39136813898894</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>3.195598627775337</v>
@@ -3988,6 +3965,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>3.290012592022761</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8.776550019971497</v>
       </c>
     </row>
     <row r="20">
@@ -3999,11 +3979,8 @@
           <t>Other invertebrates</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>0.8908864233670792</v>
+        <v>7.180750407820896</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>3.396226415094339</v>
@@ -4052,6 +4029,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>3.469709485637861</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.531646474032172</v>
       </c>
     </row>
     <row r="21">
@@ -4063,11 +4043,8 @@
           <t>Echinoderms</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>0.9691680153423203</v>
+        <v>16.68769023146598</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>13.18711273101862</v>
@@ -4116,6 +4093,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>132.7310673498428</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8.028620330629437</v>
       </c>
     </row>
     <row r="22">
@@ -4127,11 +4107,8 @@
           <t>Benthic Crustaceans</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>0.4560629446964417</v>
+        <v>10.89971010280624</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3.914260059711745</v>
@@ -4180,6 +4157,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>3.944575860818775</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.818087921027879</v>
       </c>
     </row>
     <row r="23">
@@ -4191,11 +4171,8 @@
           <t>Mollusks</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>0.4238255328272819</v>
+        <v>8.861137112999659</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1.900547727079648</v>
@@ -4244,6 +4221,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>1.952817874240082</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.144863611900174</v>
       </c>
     </row>
     <row r="24">
@@ -4255,9 +4235,6 @@
           <t>Polychaetes</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
@@ -4307,6 +4284,9 @@
         <v>0</v>
       </c>
       <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4319,11 +4299,8 @@
           <t>Zooplankton</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>1.039367493928259</v>
+        <v>8.377542142457711</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>10.21897810218978</v>
@@ -4373,6 +4350,9 @@
       <c r="V25" s="2" t="n">
         <v>10.26472130325907</v>
       </c>
+      <c r="X25" t="n">
+        <v>5.286920886370867</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -4383,9 +4363,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
@@ -4435,6 +4412,9 @@
         <v>1</v>
       </c>
       <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4449,7 +4429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4587,6 +4567,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4636,19 +4626,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4721,6 +4714,12 @@
       <c r="V3" s="2" t="n">
         <v>0.7190365959003098</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -4738,10 +4737,10 @@
         <v>846.4350018581712</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.181142965004744</v>
+        <v>1432.188935023357</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.243318464728655</v>
+        <v>6016.652795834449</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -4749,7 +4748,6 @@
       <c r="H4" s="2" t="n">
         <v>170.7387018036413</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -4788,6 +4786,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>372.1636238757835</v>
+      </c>
+      <c r="X4" t="n">
+        <v>918.709741797403</v>
       </c>
     </row>
     <row r="5">
@@ -4806,10 +4810,10 @@
         <v>1597.268427494952</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.547540625746592</v>
+        <v>2839.885998585773</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.542463161736032</v>
+        <v>11952.49988035553</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -4817,7 +4821,6 @@
       <c r="H5" s="2" t="n">
         <v>199.4890048992055</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
@@ -4856,6 +4859,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>649.9821434776145</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1566.239905925134</v>
       </c>
     </row>
     <row r="6">
@@ -4874,10 +4883,10 @@
         <v>153.9243402522635</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.374091367660116</v>
+        <v>228.0121097317405</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.412099463368281</v>
+        <v>689.3560028395739</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>70.14592862552624</v>
@@ -4926,6 +4935,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>75.50962478682321</v>
+      </c>
+      <c r="W6" t="n">
+        <v>83.30766805547835</v>
+      </c>
+      <c r="X6" t="n">
+        <v>159.8468777590228</v>
       </c>
     </row>
     <row r="7">
@@ -4944,10 +4959,10 @@
         <v>309.9904551619918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.67727191643878</v>
+        <v>484.9754816986522</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.719111357806737</v>
+        <v>1327.686817250447</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>295.3824063187016</v>
@@ -4996,6 +5011,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>290.6562923253792</v>
+      </c>
+      <c r="W7" t="n">
+        <v>154.0511161230096</v>
+      </c>
+      <c r="X7" t="n">
+        <v>293.7530857113285</v>
       </c>
     </row>
     <row r="8">
@@ -5014,10 +5035,10 @@
         <v>255.9026077261806</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.590578822776017</v>
+        <v>394.4112407436712</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.578968183579986</v>
+        <v>1021.903168236403</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>99.71095911808084</v>
@@ -5066,6 +5087,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>132.2341866875448</v>
+      </c>
+      <c r="W8" t="n">
+        <v>130.1792888268009</v>
+      </c>
+      <c r="X8" t="n">
+        <v>237.7451429923026</v>
       </c>
     </row>
     <row r="9">
@@ -5084,10 +5111,10 @@
         <v>282.5581211674234</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.635022616807587</v>
+        <v>438.8738925025881</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.7182759425584</v>
+        <v>2966.923035054145</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>272.719526869662</v>
@@ -5136,6 +5163,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>310.383756688857</v>
+      </c>
+      <c r="W9" t="n">
+        <v>142.013440766185</v>
+      </c>
+      <c r="X9" t="n">
+        <v>489.0442764319154</v>
       </c>
     </row>
     <row r="10">
@@ -5154,10 +5187,10 @@
         <v>313.2304608635627</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.68205507714256</v>
+        <v>490.4421151240603</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2.681199983511762</v>
+        <v>1404.262700088975</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>557.4982456555949</v>
@@ -5206,6 +5239,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>772.465221183781</v>
+      </c>
+      <c r="W10" t="n">
+        <v>155.4640862234754</v>
+      </c>
+      <c r="X10" t="n">
+        <v>299.2178161476036</v>
       </c>
     </row>
     <row r="11">
@@ -5224,10 +5263,10 @@
         <v>92.05696841507928</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.173560582304855</v>
+        <v>131.0055164134013</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.179921430792718</v>
+        <v>145.3624165110178</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>231.8744766013582</v>
@@ -5276,6 +5315,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>213.7976276884394</v>
+      </c>
+      <c r="W11" t="n">
+        <v>53.04537605823532</v>
+      </c>
+      <c r="X11" t="n">
+        <v>56.69730606519484</v>
       </c>
     </row>
     <row r="12">
@@ -5294,10 +5339,10 @@
         <v>120.7516739974263</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.277198391914159</v>
+        <v>175.517130737105</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.755310677303162</v>
+        <v>592.5891368001364</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>68.41420554728845</v>
@@ -5346,6 +5391,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>403.4674667799868</v>
+      </c>
+      <c r="W12" t="n">
+        <v>67.31631251775148</v>
+      </c>
+      <c r="X12" t="n">
+        <v>140.7430759851187</v>
       </c>
     </row>
     <row r="13">
@@ -5364,10 +5415,10 @@
         <v>185.4751333520175</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.451314745177743</v>
+        <v>278.7751918693182</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2.259582195110323</v>
+        <v>720.6177340049305</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>146.7371903367247</v>
@@ -5416,6 +5467,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>352.1251943066841</v>
+      </c>
+      <c r="W13" t="n">
+        <v>98.12789657363243</v>
+      </c>
+      <c r="X13" t="n">
+        <v>168.1328752678029</v>
       </c>
     </row>
     <row r="14">
@@ -5434,10 +5491,10 @@
         <v>813.3634643546879</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.159451844794102</v>
+        <v>1371.95839148301</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3.116054156501149</v>
+        <v>2592.364834979879</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>795.1394199045128</v>
@@ -5486,6 +5543,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>1012.014661583958</v>
+      </c>
+      <c r="W14" t="n">
+        <v>359.364230406349</v>
+      </c>
+      <c r="X14" t="n">
+        <v>516.6343560116387</v>
       </c>
     </row>
     <row r="15">
@@ -5504,10 +5567,10 @@
         <v>71.36619803330326</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.080611950119757</v>
+        <v>99.56333159175986</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.08495309103042</v>
+        <v>274.2746620214086</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>53.28473419439969</v>
@@ -5556,6 +5619,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>174.7858472816994</v>
+      </c>
+      <c r="W15" t="n">
+        <v>42.41902302203449</v>
+      </c>
+      <c r="X15" t="n">
+        <v>79.3496956121075</v>
       </c>
     </row>
     <row r="16">
@@ -5574,10 +5643,10 @@
         <v>78.43366965943547</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.114615033851923</v>
+        <v>110.2323166126038</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.082630257016328</v>
+        <v>150.4957089284926</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>58.74323422288015</v>
@@ -5626,6 +5695,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>61.0503588473253</v>
+      </c>
+      <c r="W16" t="n">
+        <v>46.08628653194929</v>
+      </c>
+      <c r="X16" t="n">
+        <v>55.69963957624271</v>
       </c>
     </row>
     <row r="17">
@@ -5644,10 +5719,10 @@
         <v>89.62935135809428</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.163611412396554</v>
+        <v>127.2851246109055</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.194807977247755</v>
+        <v>291.0369130204289</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>60.42991386072895</v>
@@ -5696,6 +5771,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>58.25670286460778</v>
+      </c>
+      <c r="W17" t="n">
+        <v>51.81504551421916</v>
+      </c>
+      <c r="X17" t="n">
+        <v>86.62776760765861</v>
       </c>
     </row>
     <row r="18">
@@ -5714,10 +5795,10 @@
         <v>20.60629913270001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.681031348903522</v>
+        <v>26.09254346971128</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.710844273140508</v>
+        <v>53.18453962099153</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>16.78463793307082</v>
@@ -5766,6 +5847,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>14.60679194983642</v>
+      </c>
+      <c r="W18" t="n">
+        <v>14.25048580712227</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23.09298081975728</v>
       </c>
     </row>
     <row r="19">
@@ -5784,10 +5871,10 @@
         <v>21.5728736567371</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.694312209955889</v>
+        <v>27.41432831397097</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.72758592611672</v>
+        <v>65.74305711935395</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>9.165590091570207</v>
@@ -5836,6 +5923,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>7.708260044828567</v>
+      </c>
+      <c r="W19" t="n">
+        <v>14.83580033209905</v>
+      </c>
+      <c r="X19" t="n">
+        <v>26.31853790592705</v>
       </c>
     </row>
     <row r="20">
@@ -5854,10 +5947,10 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>5.660377358490566</v>
@@ -5906,6 +5999,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>5.132941756303501</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7.552744123386954</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7.552744123386954</v>
       </c>
     </row>
     <row r="21">
@@ -5924,10 +6023,10 @@
         <v>14.10043549947644</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.575034244412934</v>
+        <v>17.33380942418715</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.49903056020661</v>
+        <v>33.3060412321109</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>23.38832915893543</v>
@@ -5976,6 +6075,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>206.4406601502191</v>
+      </c>
+      <c r="W21" t="n">
+        <v>10.21284086990289</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14.85791297816154</v>
       </c>
     </row>
     <row r="22">
@@ -5994,10 +6099,10 @@
         <v>14.1460288072336</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.575907366338125</v>
+        <v>17.39423816724682</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.594012368853116</v>
+        <v>35.50785655403004</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>10.32030415306063</v>
@@ -6046,6 +6151,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>8.592944629819488</v>
+      </c>
+      <c r="W22" t="n">
+        <v>10.24183272360691</v>
+      </c>
+      <c r="X22" t="n">
+        <v>15.85462728237232</v>
       </c>
     </row>
     <row r="23">
@@ -6064,10 +6175,10 @@
         <v>14.61028321104591</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.58466774239162</v>
+        <v>18.01041204378912</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.59692721143492</v>
+        <v>33.4471987121363</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>5.907642928647636</v>
@@ -6116,6 +6227,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>4.9179406642617</v>
+      </c>
+      <c r="W23" t="n">
+        <v>10.53640132618529</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15.63908989276836</v>
       </c>
     </row>
     <row r="24">
@@ -6134,10 +6251,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>7.818052594171997</v>
@@ -6186,6 +6303,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>5.690124008593392</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7.552744123386954</v>
+      </c>
+      <c r="X24" t="n">
+        <v>7.552744123386954</v>
       </c>
     </row>
     <row r="25">
@@ -6204,10 +6327,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>14.5985401459854</v>
@@ -6257,6 +6380,12 @@
       <c r="V25" s="2" t="n">
         <v>13.42839831858132</v>
       </c>
+      <c r="W25" t="n">
+        <v>7.552744123386954</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7.552744123386953</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -6325,6 +6454,12 @@
         <v>1</v>
       </c>
       <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6339,7 +6474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6477,6 +6612,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6526,19 +6671,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6611,6 +6759,12 @@
       <c r="V3" s="2" t="n">
         <v>0.7190365959003098</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6628,10 +6782,10 @@
         <v>846.4350018581712</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.181142965004744</v>
+        <v>1432.188935023357</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.243318464728655</v>
+        <v>6016.652795834449</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -6680,6 +6834,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>372.1636238757835</v>
+      </c>
+      <c r="X4" t="n">
+        <v>918.709741797403</v>
       </c>
     </row>
     <row r="5">
@@ -6698,10 +6858,10 @@
         <v>1597.268427494952</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.547540625746592</v>
+        <v>2839.885998585773</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.542463161736032</v>
+        <v>11952.49988035553</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -6750,6 +6910,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>649.9821434776145</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1566.239905925134</v>
       </c>
     </row>
     <row r="6">
@@ -6768,10 +6934,10 @@
         <v>153.9243402522635</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.374091367660116</v>
+        <v>228.0121097317405</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.412099463368281</v>
+        <v>689.3560028395739</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>70.14592862552624</v>
@@ -6820,6 +6986,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>75.50962478682321</v>
+      </c>
+      <c r="W6" t="n">
+        <v>83.30766805547835</v>
+      </c>
+      <c r="X6" t="n">
+        <v>159.8468777590228</v>
       </c>
     </row>
     <row r="7">
@@ -6838,10 +7010,10 @@
         <v>309.9904551619918</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.67727191643878</v>
+        <v>484.9754816986522</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2.719111357806737</v>
+        <v>1327.686817250447</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>295.3824063187016</v>
@@ -6890,6 +7062,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>290.6562923253792</v>
+      </c>
+      <c r="W7" t="n">
+        <v>154.0511161230096</v>
+      </c>
+      <c r="X7" t="n">
+        <v>293.7530857113285</v>
       </c>
     </row>
     <row r="8">
@@ -6908,10 +7086,10 @@
         <v>255.9026077261806</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.590578822776017</v>
+        <v>394.4112407436712</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.578968183579986</v>
+        <v>1021.903168236403</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>99.71095911808084</v>
@@ -6960,6 +7138,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>132.2341866875448</v>
+      </c>
+      <c r="W8" t="n">
+        <v>130.1792888268009</v>
+      </c>
+      <c r="X8" t="n">
+        <v>237.7451429923026</v>
       </c>
     </row>
     <row r="9">
@@ -6978,10 +7162,10 @@
         <v>282.5581211674234</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.635022616807587</v>
+        <v>438.8738925025881</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.7182759425584</v>
+        <v>2966.923035054145</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>272.719526869662</v>
@@ -7030,6 +7214,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>310.383756688857</v>
+      </c>
+      <c r="W9" t="n">
+        <v>142.013440766185</v>
+      </c>
+      <c r="X9" t="n">
+        <v>489.0442764319154</v>
       </c>
     </row>
     <row r="10">
@@ -7048,10 +7238,10 @@
         <v>313.2304608635627</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.68205507714256</v>
+        <v>490.4421151240603</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2.681199983511762</v>
+        <v>1404.262700088975</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>557.4982456555949</v>
@@ -7100,6 +7290,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>772.465221183781</v>
+      </c>
+      <c r="W10" t="n">
+        <v>155.4640862234754</v>
+      </c>
+      <c r="X10" t="n">
+        <v>299.2178161476036</v>
       </c>
     </row>
     <row r="11">
@@ -7118,10 +7314,10 @@
         <v>92.05696841507928</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.173560582304855</v>
+        <v>131.0055164134013</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.179921430792718</v>
+        <v>145.3624165110178</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>231.8744766013582</v>
@@ -7170,6 +7366,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>213.7976276884394</v>
+      </c>
+      <c r="W11" t="n">
+        <v>53.04537605823532</v>
+      </c>
+      <c r="X11" t="n">
+        <v>56.69730606519484</v>
       </c>
     </row>
     <row r="12">
@@ -7188,10 +7390,10 @@
         <v>120.7516739974263</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.277198391914159</v>
+        <v>175.517130737105</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.755310677303162</v>
+        <v>592.5891368001364</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>68.41420554728845</v>
@@ -7240,6 +7442,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>403.4674667799868</v>
+      </c>
+      <c r="W12" t="n">
+        <v>67.31631251775148</v>
+      </c>
+      <c r="X12" t="n">
+        <v>140.7430759851187</v>
       </c>
     </row>
     <row r="13">
@@ -7258,10 +7466,10 @@
         <v>185.4751333520175</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.451314745177743</v>
+        <v>278.7751918693182</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2.259582195110323</v>
+        <v>720.6177340049305</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>146.7371903367247</v>
@@ -7310,6 +7518,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>352.1251943066841</v>
+      </c>
+      <c r="W13" t="n">
+        <v>98.12789657363243</v>
+      </c>
+      <c r="X13" t="n">
+        <v>168.1328752678029</v>
       </c>
     </row>
     <row r="14">
@@ -7328,10 +7542,10 @@
         <v>813.3634643546879</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.159451844794102</v>
+        <v>1371.95839148301</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3.116054156501149</v>
+        <v>2592.364834979879</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>795.1394199045128</v>
@@ -7380,6 +7594,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>1012.014661583958</v>
+      </c>
+      <c r="W14" t="n">
+        <v>359.364230406349</v>
+      </c>
+      <c r="X14" t="n">
+        <v>516.6343560116387</v>
       </c>
     </row>
     <row r="15">
@@ -7398,10 +7618,10 @@
         <v>71.36619803330326</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.080611950119757</v>
+        <v>99.56333159175986</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2.08495309103042</v>
+        <v>274.2746620214086</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>53.28473419439969</v>
@@ -7450,6 +7670,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>174.7858472816994</v>
+      </c>
+      <c r="W15" t="n">
+        <v>42.41902302203449</v>
+      </c>
+      <c r="X15" t="n">
+        <v>79.3496956121075</v>
       </c>
     </row>
     <row r="16">
@@ -7468,10 +7694,10 @@
         <v>78.43366965943547</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.114615033851923</v>
+        <v>110.2323166126038</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.082630257016328</v>
+        <v>150.4957089284926</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>58.74323422288015</v>
@@ -7520,6 +7746,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>61.0503588473253</v>
+      </c>
+      <c r="W16" t="n">
+        <v>46.08628653194929</v>
+      </c>
+      <c r="X16" t="n">
+        <v>55.69963957624271</v>
       </c>
     </row>
     <row r="17">
@@ -7538,10 +7770,10 @@
         <v>89.62935135809428</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.163611412396554</v>
+        <v>127.2851246109055</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.194807977247755</v>
+        <v>291.0369130204289</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>60.42991386072895</v>
@@ -7590,6 +7822,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>58.25670286460778</v>
+      </c>
+      <c r="W17" t="n">
+        <v>51.81504551421916</v>
+      </c>
+      <c r="X17" t="n">
+        <v>86.62776760765861</v>
       </c>
     </row>
     <row r="18">
@@ -7608,10 +7846,10 @@
         <v>20.60629913270001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.681031348903522</v>
+        <v>26.09254346971128</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1.710844273140508</v>
+        <v>53.18453962099153</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>16.78463793307082</v>
@@ -7660,6 +7898,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>14.60679194983642</v>
+      </c>
+      <c r="W18" t="n">
+        <v>14.25048580712227</v>
+      </c>
+      <c r="X18" t="n">
+        <v>23.09298081975728</v>
       </c>
     </row>
     <row r="19">
@@ -7678,10 +7922,10 @@
         <v>21.5728736567371</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.694312209955889</v>
+        <v>27.41432831397097</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1.72758592611672</v>
+        <v>65.74305711935395</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>9.165590091570207</v>
@@ -7730,6 +7974,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>7.708260044828567</v>
+      </c>
+      <c r="W19" t="n">
+        <v>14.83580033209905</v>
+      </c>
+      <c r="X19" t="n">
+        <v>26.31853790592705</v>
       </c>
     </row>
     <row r="20">
@@ -7748,10 +7998,10 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>5.660377358490566</v>
@@ -7800,6 +8050,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>5.132941756303501</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7.552744123386954</v>
+      </c>
+      <c r="X20" t="n">
+        <v>7.552744123386954</v>
       </c>
     </row>
     <row r="21">
@@ -7818,10 +8074,10 @@
         <v>14.10043549947644</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.575034244412934</v>
+        <v>17.33380942418715</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.49903056020661</v>
+        <v>33.3060412321109</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>23.38832915893543</v>
@@ -7870,6 +8126,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>206.4406601502191</v>
+      </c>
+      <c r="W21" t="n">
+        <v>10.21284086990289</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14.85791297816154</v>
       </c>
     </row>
     <row r="22">
@@ -7888,10 +8150,10 @@
         <v>14.1460288072336</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.575907366338125</v>
+        <v>17.39423816724682</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1.594012368853116</v>
+        <v>35.50785655403004</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>10.32030415306063</v>
@@ -7940,6 +8202,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>8.592944629819488</v>
+      </c>
+      <c r="W22" t="n">
+        <v>10.24183272360691</v>
+      </c>
+      <c r="X22" t="n">
+        <v>15.85462728237232</v>
       </c>
     </row>
     <row r="23">
@@ -7958,10 +8226,10 @@
         <v>14.61028321104591</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.58466774239162</v>
+        <v>18.01041204378912</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1.59692721143492</v>
+        <v>33.4471987121363</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>5.907642928647636</v>
@@ -8010,6 +8278,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>4.9179406642617</v>
+      </c>
+      <c r="W23" t="n">
+        <v>10.53640132618529</v>
+      </c>
+      <c r="X23" t="n">
+        <v>15.63908989276836</v>
       </c>
     </row>
     <row r="24">
@@ -8028,10 +8302,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>7.818052594171997</v>
@@ -8080,6 +8354,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>5.690124008593392</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7.552744123386954</v>
+      </c>
+      <c r="X24" t="n">
+        <v>7.552744123386954</v>
       </c>
     </row>
     <row r="25">
@@ -8098,10 +8378,10 @@
         <v>10</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1.484810705611799</v>
+        <v>11.96791734636816</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>14.5985401459854</v>
@@ -8151,6 +8431,12 @@
       <c r="V25" s="2" t="n">
         <v>13.42839831858132</v>
       </c>
+      <c r="W25" t="n">
+        <v>7.552744123386954</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7.552744123386953</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -8219,6 +8505,12 @@
         <v>1</v>
       </c>
       <c r="V26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8691,7 +8983,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.19875674399437</v>
       </c>
@@ -8817,7 +9108,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>East_China_Sea (2018)</t>
@@ -8881,7 +9171,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -8921,7 +9210,6 @@
       <c r="AP3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
@@ -9073,7 +9361,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.2183101495339221</v>
       </c>
@@ -9175,7 +9462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9236,14 +9523,12 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>3574.8</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9257,14 +9542,12 @@
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>3574.8</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9278,14 +9561,12 @@
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>3574.8</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9709,6 +9990,50 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3574.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3574.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9845,7 +10170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9881,7 +10206,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -9894,7 +10218,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -9907,7 +10230,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -9920,7 +10242,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -9933,7 +10254,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -9946,7 +10266,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -9959,7 +10278,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -9972,7 +10290,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -9985,7 +10302,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -10029,7 +10345,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10046,7 +10362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10322,6 +10638,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
